--- a/OLD/simple.xlsx.xlsx
+++ b/OLD/simple.xlsx.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,6 +474,11 @@
           <t>evaluation</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>correctness_%</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -481,42 +486,45 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[(7, 0), (8, 1), (9, 2), (10, 3)]</t>
+          <t>[(6, 3), (7, 2)]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>3.999051653091517</v>
+        <v>3.259676255366241</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>GTCAAGTGTCA</t>
+          <t>CAAGTG</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>GTCA</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>GTCA</t>
+          <t>TG</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;AGT&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;AG&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.6587365053978409</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Confirmed DR</t>
-        </is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="3">
@@ -525,86 +533,45 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[(5, 0), (6, 1)]</t>
+          <t>[(9, 7), (10, 6)]</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>1.950507368957596</v>
+        <v>3.173943943708315</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>GTCAAGT</t>
+          <t>TGTCA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>TG</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;CAA&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;T&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.7191123550579768</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Confirmed DR</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>[(7, 5), (8, 6)]</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1.954029753256627</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>GTGT</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>GT</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>GT</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Confirmed DR</t>
-        </is>
+          <t>Confirmed IR</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/OLD/simple.xlsx.xlsx
+++ b/OLD/simple.xlsx.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,91 +486,44 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[(6, 3), (7, 2)]</t>
+          <t>[(8, 1), (9, 2), (10, 3)]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.259676255366241</v>
+        <v>5.57233498624647</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>CAAGTG</t>
+          <t>TCAAGTGTCA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>TCA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>TG</t>
+          <t>TCA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;AG&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;</t>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;AGTG&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.6587365053978409</v>
+        <v>0.007996801279488205</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Confirmed IR</t>
+          <t>Confirmed DR</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>[(9, 7), (10, 6)]</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" t="n">
-        <v>3.173943943708315</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>TGTCA</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>TG</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;T&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>0.7191123550579768</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Confirmed IR</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
         <v>100</v>
       </c>
     </row>
